--- a/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_9_42.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.2/Output_9_42.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3409383.021783933</v>
+        <v>3445741.068091148</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>603.5370117048578</v>
+        <v>603.5370117101819</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>603.5370117048578</v>
+        <v>603.5370117101819</v>
       </c>
     </row>
     <row r="11">
@@ -739,16 +739,16 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>152.5766849062232</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -790,10 +790,10 @@
         <v>4.473444462796863</v>
       </c>
       <c r="U3" t="n">
-        <v>124.0690072200682</v>
+        <v>0.1959257979225981</v>
       </c>
       <c r="V3" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -909,10 +909,10 @@
         <v>3.347322035759929</v>
       </c>
       <c r="H5" t="n">
-        <v>5.608919435675665</v>
+        <v>3.810231567849018</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.798687867826647</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>374</v>
+        <v>133.6519859716246</v>
       </c>
       <c r="S6" t="n">
         <v>62.48881128536602</v>
@@ -1027,19 +1027,19 @@
         <v>4.473444462796834</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1959257979225968</v>
+        <v>374</v>
       </c>
       <c r="V6" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
+        <v>32.37314290982852</v>
+      </c>
+      <c r="X6" t="n">
         <v>374</v>
       </c>
-      <c r="X6" t="n">
-        <v>133.8587497479445</v>
-      </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>104.8016313460113</v>
       </c>
     </row>
     <row r="7">
@@ -1149,7 +1149,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.79868786782652</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1179,7 +1179,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>87.30283556964716</v>
+        <v>85.50414770182039</v>
       </c>
       <c r="T8" t="n">
         <v>184.8805867536895</v>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>128.9709564352693</v>
       </c>
       <c r="C9" t="n">
         <v>361.0999124455193</v>
@@ -1216,10 +1216,10 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>132.0068113193051</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>133.6519859716245</v>
@@ -1450,13 +1450,13 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
         <v>3.99961134672543</v>
@@ -1465,7 +1465,7 @@
         <v>4.021973978873973</v>
       </c>
       <c r="I12" t="n">
-        <v>173.591815881973</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R12" t="n">
         <v>180.333570877285</v>
@@ -1501,16 +1501,16 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U12" t="n">
-        <v>79.16168051490371</v>
+        <v>174.1249482875295</v>
       </c>
       <c r="V12" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W12" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>98.86273944538755</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y12" t="n">
         <v>78.39139276613435</v>
@@ -1562,7 +1562,7 @@
         <v>155.2579933044718</v>
       </c>
       <c r="O13" t="n">
-        <v>230.9267936392535</v>
+        <v>231.765039488851</v>
       </c>
       <c r="P13" t="n">
         <v>291.4220612627038</v>
@@ -1574,7 +1574,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S13" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243831</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1681,28 +1681,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C15" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E15" t="n">
         <v>21.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>339.6362423378769</v>
+        <v>192.2280582198495</v>
       </c>
       <c r="G15" t="n">
         <v>3.99961134672543</v>
       </c>
       <c r="H15" t="n">
-        <v>228.3343275582644</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I15" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1726,7 +1726,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>180.333570877285</v>
@@ -1750,7 +1750,7 @@
         <v>98.86273944538755</v>
       </c>
       <c r="Y15" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1790,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M16" t="n">
-        <v>101.5541524381981</v>
+        <v>102.3923982877958</v>
       </c>
       <c r="N16" t="n">
         <v>155.2579933044718</v>
@@ -1857,10 +1857,10 @@
         <v>81.3744577141519</v>
       </c>
       <c r="H17" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949504</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4605873653143577</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1918,16 +1918,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>63.55655664632661</v>
+        <v>237.1483725282995</v>
       </c>
       <c r="C18" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>26.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F18" t="n">
         <v>18.63624233787687</v>
@@ -1975,7 +1975,7 @@
         <v>81.3753501231742</v>
       </c>
       <c r="U18" t="n">
-        <v>79.16168051490371</v>
+        <v>400.1616805149037</v>
       </c>
       <c r="V18" t="n">
         <v>93.51066719152016</v>
@@ -1984,10 +1984,10 @@
         <v>111.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>272.4545553273604</v>
+        <v>98.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M19" t="n">
         <v>102.3923982877958</v>
@@ -2042,7 +2042,7 @@
         <v>291.4220612627038</v>
       </c>
       <c r="Q19" t="n">
-        <v>352.0570205760006</v>
+        <v>352.895266425598</v>
       </c>
       <c r="R19" t="n">
         <v>377.7099312598395</v>
@@ -2091,13 +2091,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H20" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.4605873653141466</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>142.3350019731772</v>
@@ -2161,19 +2161,19 @@
         <v>40.09991244551929</v>
       </c>
       <c r="D21" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E21" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F21" t="n">
-        <v>18.63624233787687</v>
+        <v>192.2280582198502</v>
       </c>
       <c r="G21" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H21" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2206,19 +2206,19 @@
         <v>180.333570877285</v>
       </c>
       <c r="S21" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T21" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U21" t="n">
-        <v>252.7534963968766</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V21" t="n">
-        <v>414.5106671915202</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X21" t="n">
         <v>419.8627394453875</v>
@@ -2264,7 +2264,7 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M22" t="n">
         <v>102.3923982877958</v>
@@ -2276,16 +2276,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P22" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q22" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S22" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,13 +2328,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H23" t="n">
-        <v>73.30747219949482</v>
+        <v>72.84688483418068</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.4605873653143577</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2392,25 +2392,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C24" t="n">
         <v>40.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
-        <v>324.9996113467254</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H24" t="n">
-        <v>4.021973978873961</v>
+        <v>98.98524175149967</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2437,25 +2437,25 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R24" t="n">
         <v>180.333570877285</v>
       </c>
       <c r="S24" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T24" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U24" t="n">
-        <v>252.7534963968768</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V24" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W24" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X24" t="n">
         <v>98.86273944538755</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M25" t="n">
         <v>102.3923982877958</v>
@@ -2513,16 +2513,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P25" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q25" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>377.7099312598396</v>
+        <v>376.871685410242</v>
       </c>
       <c r="S25" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C27" t="n">
-        <v>40.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D27" t="n">
-        <v>26.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
         <v>21.67209722191262</v>
@@ -2644,13 +2644,13 @@
         <v>18.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>3.99961134672543</v>
+        <v>98.96287911935113</v>
       </c>
       <c r="H27" t="n">
         <v>4.021973978873973</v>
       </c>
       <c r="I27" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2674,10 +2674,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R27" t="n">
-        <v>483.2744725660224</v>
+        <v>180.333570877285</v>
       </c>
       <c r="S27" t="n">
         <v>131.8202263797057</v>
@@ -2689,10 +2689,10 @@
         <v>79.16168051490371</v>
       </c>
       <c r="V27" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W27" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X27" t="n">
         <v>98.86273944538755</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>10.32179209220538</v>
+        <v>9.483546242607703</v>
       </c>
       <c r="M28" t="n">
         <v>102.3923982877958</v>
@@ -2759,7 +2759,7 @@
         <v>377.7099312598395</v>
       </c>
       <c r="S28" t="n">
-        <v>29.72461090243831</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,10 +2802,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H29" t="n">
-        <v>72.84688483418068</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0.4605873653139497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>142.3350019731772</v>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C30" t="n">
         <v>361.0999124455193</v>
@@ -2875,16 +2875,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>342.6720972219126</v>
+        <v>21.67209722191262</v>
       </c>
       <c r="F30" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H30" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2917,25 +2917,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S30" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T30" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U30" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V30" t="n">
-        <v>267.1024830734931</v>
+        <v>267.1024830734935</v>
       </c>
       <c r="W30" t="n">
-        <v>111.3731429098285</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X30" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y30" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="31">
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M31" t="n">
         <v>102.3923982877958</v>
@@ -2987,16 +2987,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P31" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q31" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>376.871685410242</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S31" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3030,7 +3030,7 @@
         <v>128.4745782429939</v>
       </c>
       <c r="D32" t="n">
-        <v>89.79974310516415</v>
+        <v>89.33915573984979</v>
       </c>
       <c r="E32" t="n">
         <v>83.36328960686865</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>142.3350019731772</v>
+        <v>142.7955893384911</v>
       </c>
       <c r="T32" t="n">
         <v>259.6218731858503</v>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>237.1483725282995</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C33" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D33" t="n">
         <v>347.9376868977026</v>
@@ -3115,13 +3115,13 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F33" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G33" t="n">
         <v>3.99961134672543</v>
       </c>
       <c r="H33" t="n">
-        <v>4.021973978873973</v>
+        <v>177.6137898608468</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
         <v>10.32179209220538</v>
       </c>
       <c r="M34" t="n">
-        <v>101.5541524381981</v>
+        <v>102.3923982877958</v>
       </c>
       <c r="N34" t="n">
         <v>155.2579933044718</v>
@@ -3227,7 +3227,7 @@
         <v>291.4220612627038</v>
       </c>
       <c r="Q34" t="n">
-        <v>352.895266425598</v>
+        <v>352.0570205760006</v>
       </c>
       <c r="R34" t="n">
         <v>377.7099312598395</v>
@@ -3276,7 +3276,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G35" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H35" t="n">
         <v>72.84688483418068</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S35" t="n">
         <v>142.3350019731772</v>
@@ -3318,7 +3318,7 @@
         <v>259.6218731858503</v>
       </c>
       <c r="U35" t="n">
-        <v>328.5712507480957</v>
+        <v>328.1106633827815</v>
       </c>
       <c r="V35" t="n">
         <v>308.8510241668239</v>
@@ -3340,25 +3340,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>384.5565566463266</v>
+        <v>63.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>213.6917283274922</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D36" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E36" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H36" t="n">
-        <v>4.021973978873973</v>
+        <v>177.6137898608472</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -3391,25 +3391,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S36" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T36" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U36" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V36" t="n">
-        <v>93.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W36" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X36" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y36" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="37">
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M37" t="n">
         <v>102.3923982877958</v>
@@ -3461,16 +3461,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P37" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q37" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>377.7099312598395</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S37" t="n">
-        <v>29.72461090243831</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3513,13 +3513,13 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G38" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H38" t="n">
         <v>72.84688483418068</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4605873653141466</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S38" t="n">
         <v>142.3350019731772</v>
@@ -3580,7 +3580,7 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D39" t="n">
         <v>26.93768689770263</v>
@@ -3589,16 +3589,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>18.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G39" t="n">
-        <v>177.5914272286988</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H39" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3628,25 +3628,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S39" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T39" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U39" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V39" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>111.3731429098285</v>
+        <v>414.3140445985663</v>
       </c>
       <c r="X39" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>399.3913927661343</v>
+        <v>78.39139276613435</v>
       </c>
     </row>
     <row r="40">
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M40" t="n">
         <v>102.3923982877958</v>
@@ -3698,16 +3698,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P40" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q40" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>377.7099312598396</v>
+        <v>376.871685410242</v>
       </c>
       <c r="S40" t="n">
-        <v>29.72461090243842</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3750,10 +3750,10 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G41" t="n">
-        <v>81.3744577141519</v>
+        <v>81.37445771415189</v>
       </c>
       <c r="H41" t="n">
-        <v>73.30747219949504</v>
+        <v>73.30747219949482</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3817,25 +3817,25 @@
         <v>63.55655664632661</v>
       </c>
       <c r="C42" t="n">
-        <v>361.0999124455193</v>
+        <v>40.09991244551929</v>
       </c>
       <c r="D42" t="n">
         <v>26.93768689770263</v>
       </c>
       <c r="E42" t="n">
-        <v>21.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>3.99961134672543</v>
+        <v>3.999611346725456</v>
       </c>
       <c r="H42" t="n">
-        <v>4.021973978873973</v>
+        <v>4.021973978873961</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3859,25 +3859,25 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R42" t="n">
-        <v>180.333570877285</v>
+        <v>404.6459244566755</v>
       </c>
       <c r="S42" t="n">
-        <v>131.8202263797057</v>
+        <v>131.8202263797056</v>
       </c>
       <c r="T42" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U42" t="n">
-        <v>79.16168051490371</v>
+        <v>79.16168051490372</v>
       </c>
       <c r="V42" t="n">
-        <v>267.1024830734931</v>
+        <v>93.51066719152016</v>
       </c>
       <c r="W42" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>98.86273944538755</v>
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>10.32179209220538</v>
+        <v>10.3217920922054</v>
       </c>
       <c r="M43" t="n">
         <v>102.3923982877958</v>
@@ -3935,16 +3935,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P43" t="n">
-        <v>291.4220612627038</v>
+        <v>291.4220612627037</v>
       </c>
       <c r="Q43" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>376.871685410242</v>
+        <v>377.7099312598396</v>
       </c>
       <c r="S43" t="n">
-        <v>30.56285675203577</v>
+        <v>29.72461090243842</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
         <v>83.88962870801186</v>
       </c>
       <c r="G44" t="n">
-        <v>81.37445771415189</v>
+        <v>81.3744577141519</v>
       </c>
       <c r="H44" t="n">
         <v>72.84688483418068</v>
@@ -4020,10 +4020,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>0.4605873653139497</v>
       </c>
       <c r="S44" t="n">
-        <v>142.7955893384911</v>
+        <v>142.3350019731772</v>
       </c>
       <c r="T44" t="n">
         <v>259.6218731858503</v>
@@ -4060,16 +4060,16 @@
         <v>26.93768689770263</v>
       </c>
       <c r="E45" t="n">
-        <v>195.2639131038858</v>
+        <v>195.2639131038853</v>
       </c>
       <c r="F45" t="n">
         <v>18.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>3.999611346725456</v>
+        <v>3.99961134672543</v>
       </c>
       <c r="H45" t="n">
-        <v>4.021973978873961</v>
+        <v>4.021973978873973</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -4102,25 +4102,25 @@
         <v>180.333570877285</v>
       </c>
       <c r="S45" t="n">
-        <v>131.8202263797056</v>
+        <v>131.8202263797057</v>
       </c>
       <c r="T45" t="n">
         <v>81.3753501231742</v>
       </c>
       <c r="U45" t="n">
-        <v>79.16168051490372</v>
+        <v>79.16168051490371</v>
       </c>
       <c r="V45" t="n">
         <v>93.51066719152016</v>
       </c>
       <c r="W45" t="n">
-        <v>432.3731429098285</v>
+        <v>111.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>98.86273944538755</v>
       </c>
       <c r="Y45" t="n">
-        <v>78.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4160,7 +4160,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>10.3217920922054</v>
+        <v>10.32179209220538</v>
       </c>
       <c r="M46" t="n">
         <v>102.3923982877958</v>
@@ -4172,16 +4172,16 @@
         <v>231.765039488851</v>
       </c>
       <c r="P46" t="n">
-        <v>291.4220612627037</v>
+        <v>291.4220612627038</v>
       </c>
       <c r="Q46" t="n">
         <v>352.895266425598</v>
       </c>
       <c r="R46" t="n">
-        <v>377.7099312598396</v>
+        <v>376.871685410242</v>
       </c>
       <c r="S46" t="n">
-        <v>29.72461090252711</v>
+        <v>30.56285675203577</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4321,22 +4321,22 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>400.18</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L2" t="n">
-        <v>464.2419149748744</v>
+        <v>822.0783303517587</v>
       </c>
       <c r="M2" t="n">
-        <v>755.48</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="N2" t="n">
-        <v>755.48</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="O2" t="n">
-        <v>1125.74</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P2" t="n">
         <v>1496</v>
@@ -4376,19 +4376,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>590.9569085489952</v>
+        <v>1079.201771408213</v>
       </c>
       <c r="C3" t="n">
-        <v>590.9569085489952</v>
+        <v>1079.201771408213</v>
       </c>
       <c r="D3" t="n">
-        <v>590.9569085489952</v>
+        <v>727.7495624206344</v>
       </c>
       <c r="E3" t="n">
-        <v>244.8234770117097</v>
+        <v>727.7495624206344</v>
       </c>
       <c r="F3" t="n">
-        <v>244.8234770117097</v>
+        <v>573.6316988789948</v>
       </c>
       <c r="G3" t="n">
         <v>244.8234770117097</v>
@@ -4433,19 +4433,19 @@
         <v>1146.820433372515</v>
       </c>
       <c r="U3" t="n">
-        <v>1021.498203857294</v>
+        <v>1146.622528526128</v>
       </c>
       <c r="V3" t="n">
-        <v>643.7204260795165</v>
+        <v>1131.965288938734</v>
       </c>
       <c r="W3" t="n">
-        <v>611.0202817261544</v>
+        <v>1099.265144585372</v>
       </c>
       <c r="X3" t="n">
-        <v>590.9569085489952</v>
+        <v>1079.201771408213</v>
       </c>
       <c r="Y3" t="n">
-        <v>590.9569085489952</v>
+        <v>1079.201771408213</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1210.2445873942</v>
+        <v>1028.614002149153</v>
       </c>
       <c r="C4" t="n">
-        <v>1210.2445873942</v>
+        <v>1028.614002149153</v>
       </c>
       <c r="D4" t="n">
-        <v>1210.2445873942</v>
+        <v>1028.614002149153</v>
       </c>
       <c r="E4" t="n">
-        <v>1210.2445873942</v>
+        <v>1028.614002149153</v>
       </c>
       <c r="F4" t="n">
-        <v>1210.2445873942</v>
+        <v>1028.614002149153</v>
       </c>
       <c r="G4" t="n">
-        <v>1210.2445873942</v>
+        <v>1028.614002149153</v>
       </c>
       <c r="H4" t="n">
-        <v>1381.38016337327</v>
+        <v>1028.614002149153</v>
       </c>
       <c r="I4" t="n">
-        <v>1381.38016337327</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="J4" t="n">
-        <v>1386.743548464727</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K4" t="n">
         <v>1386.743548464727</v>
@@ -4506,25 +4506,25 @@
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T4" t="n">
-        <v>218.7737217817557</v>
+        <v>259.1973975316665</v>
       </c>
       <c r="U4" t="n">
-        <v>465.3348468790587</v>
+        <v>505.7585226289696</v>
       </c>
       <c r="V4" t="n">
-        <v>664.1562397650047</v>
+        <v>704.5799155149155</v>
       </c>
       <c r="W4" t="n">
-        <v>836.0471580246821</v>
+        <v>876.4708337745928</v>
       </c>
       <c r="X4" t="n">
-        <v>987.0779490488756</v>
+        <v>916.8566644828607</v>
       </c>
       <c r="Y4" t="n">
-        <v>1098.487249727908</v>
+        <v>916.8566644828607</v>
       </c>
     </row>
     <row r="5">
@@ -4552,22 +4552,22 @@
         <v>35.58557518755118</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.73685643214813</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
-        <v>327.1281081337421</v>
+        <v>29.92</v>
       </c>
       <c r="K5" t="n">
-        <v>697.3881081337421</v>
+        <v>327.128108133742</v>
       </c>
       <c r="L5" t="n">
+        <v>697.388108133742</v>
+      </c>
+      <c r="M5" t="n">
         <v>1067.648108133742</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1437.908108133742</v>
       </c>
       <c r="N5" t="n">
         <v>1437.908108133742</v>
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>372.9869114524009</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="C6" t="n">
-        <v>372.9869114524009</v>
+        <v>381.3722089875785</v>
       </c>
       <c r="D6" t="n">
-        <v>372.9869114524009</v>
+        <v>29.92</v>
       </c>
       <c r="E6" t="n">
-        <v>372.9869114524009</v>
+        <v>29.92</v>
       </c>
       <c r="F6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1346.247111942856</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R6" t="n">
-        <v>968.469334165078</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S6" t="n">
-        <v>905.3493227657183</v>
+        <v>1294.664012937232</v>
       </c>
       <c r="T6" t="n">
-        <v>900.8306919952164</v>
+        <v>1290.14538216673</v>
       </c>
       <c r="U6" t="n">
-        <v>900.6327871488299</v>
+        <v>912.3676043889523</v>
       </c>
       <c r="V6" t="n">
-        <v>885.9755475614359</v>
+        <v>897.7103648015582</v>
       </c>
       <c r="W6" t="n">
-        <v>508.197769783658</v>
+        <v>865.010220448196</v>
       </c>
       <c r="X6" t="n">
-        <v>372.9869114524009</v>
+        <v>487.2324426704182</v>
       </c>
       <c r="Y6" t="n">
-        <v>372.9869114524009</v>
+        <v>381.3722089875785</v>
       </c>
     </row>
     <row r="7">
@@ -4692,22 +4692,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>457.9394678150667</v>
+        <v>656.6616989445531</v>
       </c>
       <c r="C7" t="n">
-        <v>457.9394678150667</v>
+        <v>782.6637047629889</v>
       </c>
       <c r="D7" t="n">
-        <v>457.9394678150667</v>
+        <v>782.6637047629889</v>
       </c>
       <c r="E7" t="n">
-        <v>575.7683720264797</v>
+        <v>900.4926089744019</v>
       </c>
       <c r="F7" t="n">
-        <v>700.1293446184152</v>
+        <v>1024.853581566337</v>
       </c>
       <c r="G7" t="n">
-        <v>853.7180055872677</v>
+        <v>1024.853581566337</v>
       </c>
       <c r="H7" t="n">
         <v>1024.853581566337</v>
@@ -4746,22 +4746,22 @@
         <v>70.34367574991083</v>
       </c>
       <c r="T7" t="n">
-        <v>70.34367574991083</v>
+        <v>147.3124451567644</v>
       </c>
       <c r="U7" t="n">
-        <v>70.34367574991083</v>
+        <v>393.8735702540674</v>
       </c>
       <c r="V7" t="n">
-        <v>70.34367574991083</v>
+        <v>393.8735702540674</v>
       </c>
       <c r="W7" t="n">
-        <v>242.2345940095882</v>
+        <v>393.8735702540674</v>
       </c>
       <c r="X7" t="n">
-        <v>242.2345940095882</v>
+        <v>544.9043612782609</v>
       </c>
       <c r="Y7" t="n">
-        <v>353.6438946886205</v>
+        <v>544.9043612782609</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106.914147375084</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C8" t="n">
-        <v>56.9398259175144</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D8" t="n">
-        <v>46.49623426110047</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E8" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F8" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G8" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H8" t="n">
-        <v>29.92</v>
+        <v>31.736856432148</v>
       </c>
       <c r="I8" t="n">
         <v>29.92</v>
@@ -4807,13 +4807,13 @@
         <v>886.1402453266331</v>
       </c>
       <c r="N8" t="n">
-        <v>1067.648108133742</v>
+        <v>1256.400245326633</v>
       </c>
       <c r="O8" t="n">
-        <v>1067.648108133742</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P8" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
@@ -4822,25 +4822,25 @@
         <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T8" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U8" t="n">
-        <v>969.3617021698518</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V8" t="n">
-        <v>737.1889504861913</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W8" t="n">
-        <v>496.4076616165473</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X8" t="n">
-        <v>302.1835874138526</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y8" t="n">
-        <v>189.7417362190987</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="9">
@@ -4850,16 +4850,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1089.186506748585</v>
+        <v>1092.253026833469</v>
       </c>
       <c r="C9" t="n">
-        <v>724.4391204399794</v>
+        <v>727.505640524864</v>
       </c>
       <c r="D9" t="n">
-        <v>372.9869114524009</v>
+        <v>376.0534315372855</v>
       </c>
       <c r="E9" t="n">
-        <v>372.9869114524009</v>
+        <v>29.92</v>
       </c>
       <c r="F9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1359.445816914692</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1224.443810882748</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S9" t="n">
-        <v>1161.323799483389</v>
+        <v>1294.664012937232</v>
       </c>
       <c r="T9" t="n">
-        <v>1156.805168712887</v>
+        <v>1290.14538216673</v>
       </c>
       <c r="U9" t="n">
-        <v>1156.6072638665</v>
+        <v>1289.947477320344</v>
       </c>
       <c r="V9" t="n">
-        <v>1141.950024279106</v>
+        <v>1275.29023773295</v>
       </c>
       <c r="W9" t="n">
-        <v>1109.249879925744</v>
+        <v>1242.590093379587</v>
       </c>
       <c r="X9" t="n">
-        <v>1089.186506748585</v>
+        <v>1222.526720202428</v>
       </c>
       <c r="Y9" t="n">
-        <v>1089.186506748585</v>
+        <v>1222.526720202428</v>
       </c>
     </row>
     <row r="10">
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>576.0083476291953</v>
+        <v>292.3600917032257</v>
       </c>
       <c r="C10" t="n">
-        <v>702.0103534476311</v>
+        <v>418.3620975216616</v>
       </c>
       <c r="D10" t="n">
-        <v>815.3294975726312</v>
+        <v>418.3620975216616</v>
       </c>
       <c r="E10" t="n">
-        <v>815.3294975726312</v>
+        <v>418.3620975216616</v>
       </c>
       <c r="F10" t="n">
-        <v>939.6904701645667</v>
+        <v>542.723070113597</v>
       </c>
       <c r="G10" t="n">
-        <v>939.6904701645667</v>
+        <v>542.723070113597</v>
       </c>
       <c r="H10" t="n">
-        <v>1024.853581566338</v>
+        <v>713.8586460926667</v>
       </c>
       <c r="I10" t="n">
-        <v>1251.462556240126</v>
+        <v>940.4676207664545</v>
       </c>
       <c r="J10" t="n">
         <v>1251.462556240126</v>
@@ -4992,13 +4992,13 @@
         <v>29.92</v>
       </c>
       <c r="W10" t="n">
-        <v>201.8109182596774</v>
+        <v>29.92</v>
       </c>
       <c r="X10" t="n">
-        <v>352.841709283871</v>
+        <v>180.9507910241935</v>
       </c>
       <c r="Y10" t="n">
-        <v>464.2510099629032</v>
+        <v>292.3600917032257</v>
       </c>
     </row>
     <row r="11">
@@ -5032,13 +5032,13 @@
         <v>51.92</v>
       </c>
       <c r="J11" t="n">
-        <v>559.4285273090126</v>
+        <v>310.7478922784252</v>
       </c>
       <c r="K11" t="n">
-        <v>1201.938527309012</v>
+        <v>953.2578922784252</v>
       </c>
       <c r="L11" t="n">
-        <v>1844.448527309012</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="M11" t="n">
         <v>2238.277892278425</v>
@@ -5087,25 +5087,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>668.0405455662462</v>
+        <v>816.937701241021</v>
       </c>
       <c r="C12" t="n">
-        <v>627.5355835000652</v>
+        <v>776.43273917484</v>
       </c>
       <c r="D12" t="n">
-        <v>600.325798754911</v>
+        <v>424.9805301872616</v>
       </c>
       <c r="E12" t="n">
-        <v>254.1923672176255</v>
+        <v>403.0895228924003</v>
       </c>
       <c r="F12" t="n">
-        <v>235.3678800076489</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G12" t="n">
-        <v>231.3278685463101</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H12" t="n">
-        <v>227.2652685676495</v>
+        <v>51.92</v>
       </c>
       <c r="I12" t="n">
         <v>51.92</v>
@@ -5132,31 +5132,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q12" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R12" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S12" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T12" t="n">
-        <v>1846.683151095641</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U12" t="n">
-        <v>1766.721857646244</v>
+        <v>1591.376589078594</v>
       </c>
       <c r="V12" t="n">
-        <v>1348.024214018445</v>
+        <v>1496.92136969322</v>
       </c>
       <c r="W12" t="n">
-        <v>911.2836656246791</v>
+        <v>1384.423245541878</v>
       </c>
       <c r="X12" t="n">
-        <v>811.4223126495401</v>
+        <v>960.3194683243149</v>
       </c>
       <c r="Y12" t="n">
-        <v>732.2390876332428</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="13">
@@ -5205,16 +5205,16 @@
         <v>1348.401726605486</v>
       </c>
       <c r="O13" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P13" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q13" t="n">
-        <v>464.3167555675508</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R13" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741244</v>
       </c>
       <c r="S13" t="n">
         <v>51.92</v>
@@ -5272,13 +5272,13 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K14" t="n">
-        <v>1009.32297330616</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L14" t="n">
-        <v>1651.83297330616</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M14" t="n">
-        <v>1651.83297330616</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N14" t="n">
         <v>1651.83297330616</v>
@@ -5324,25 +5324,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1237.102618183067</v>
+        <v>668.040545566246</v>
       </c>
       <c r="C15" t="n">
-        <v>1196.597656116886</v>
+        <v>303.2931592576406</v>
       </c>
       <c r="D15" t="n">
-        <v>845.1454471293077</v>
+        <v>276.0833745124864</v>
       </c>
       <c r="E15" t="n">
-        <v>823.2544398344465</v>
+        <v>254.1923672176252</v>
       </c>
       <c r="F15" t="n">
-        <v>480.1875283820456</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G15" t="n">
-        <v>476.1475169207068</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H15" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I15" t="n">
         <v>51.92</v>
@@ -5369,31 +5369,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q15" t="n">
-        <v>2164.764564500508</v>
+        <v>2244.187340368535</v>
       </c>
       <c r="R15" t="n">
-        <v>1982.60944240224</v>
+        <v>2062.032218270268</v>
       </c>
       <c r="S15" t="n">
-        <v>1849.457698584356</v>
+        <v>1928.880474452383</v>
       </c>
       <c r="T15" t="n">
-        <v>1767.260375227614</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U15" t="n">
-        <v>1687.299081778216</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V15" t="n">
-        <v>1592.843862392842</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W15" t="n">
-        <v>1480.3457382415</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X15" t="n">
-        <v>1380.484385266361</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y15" t="n">
-        <v>1301.301160250064</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="16">
@@ -5433,7 +5433,7 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L16" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M16" t="n">
         <v>1506.07469544798</v>
@@ -5500,7 +5500,7 @@
         <v>125.9679517166617</v>
       </c>
       <c r="H17" t="n">
-        <v>52.3852397629438</v>
+        <v>51.92</v>
       </c>
       <c r="I17" t="n">
         <v>51.92</v>
@@ -5515,13 +5515,13 @@
         <v>523.631587033441</v>
       </c>
       <c r="M17" t="n">
-        <v>563.4049796447796</v>
+        <v>527.9430746891146</v>
       </c>
       <c r="N17" t="n">
-        <v>1205.91497964478</v>
+        <v>1170.453074689115</v>
       </c>
       <c r="O17" t="n">
-        <v>1367.045081027735</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P17" t="n">
         <v>2009.555081027735</v>
@@ -5561,13 +5561,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1141.180125483445</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C18" t="n">
-        <v>776.43273917484</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D18" t="n">
-        <v>424.9805301872615</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E18" t="n">
         <v>78.84709864997603</v>
@@ -5618,19 +5618,19 @@
         <v>1846.683151095641</v>
       </c>
       <c r="U18" t="n">
-        <v>1766.721857646244</v>
+        <v>1442.479433403819</v>
       </c>
       <c r="V18" t="n">
-        <v>1672.26663826087</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W18" t="n">
-        <v>1559.768514109528</v>
+        <v>1235.526089867103</v>
       </c>
       <c r="X18" t="n">
-        <v>1284.561892566739</v>
+        <v>1135.664736891964</v>
       </c>
       <c r="Y18" t="n">
-        <v>1205.378667550442</v>
+        <v>732.2390876332428</v>
       </c>
     </row>
     <row r="19">
@@ -5670,19 +5670,19 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L19" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M19" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N19" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O19" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P19" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q19" t="n">
         <v>464.3167555675508</v>
@@ -5719,46 +5719,46 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C20" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D20" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E20" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F20" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G20" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H20" t="n">
-        <v>51.92</v>
+        <v>52.38523976294358</v>
       </c>
       <c r="I20" t="n">
         <v>51.92</v>
       </c>
       <c r="J20" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K20" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L20" t="n">
-        <v>991.9887866314309</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M20" t="n">
-        <v>991.9887866314309</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N20" t="n">
-        <v>991.9887866314309</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O20" t="n">
-        <v>1367.045081027735</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P20" t="n">
         <v>2009.555081027735</v>
@@ -5767,28 +5767,28 @@
         <v>2596</v>
       </c>
       <c r="R20" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S20" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T20" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U20" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V20" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W20" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X20" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y20" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="21">
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>168.4528527561725</v>
+        <v>992.2829698086708</v>
       </c>
       <c r="C21" t="n">
-        <v>127.9478906899915</v>
+        <v>951.7780077424898</v>
       </c>
       <c r="D21" t="n">
-        <v>100.7381059448373</v>
+        <v>600.3257987549114</v>
       </c>
       <c r="E21" t="n">
-        <v>78.84709864997603</v>
+        <v>254.1923672176259</v>
       </c>
       <c r="F21" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G21" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H21" t="n">
         <v>51.92</v>
@@ -5852,22 +5852,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T21" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U21" t="n">
-        <v>1591.376589078594</v>
+        <v>1766.721857646244</v>
       </c>
       <c r="V21" t="n">
-        <v>1172.678945450796</v>
+        <v>1672.26663826087</v>
       </c>
       <c r="W21" t="n">
-        <v>735.9383970570298</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X21" t="n">
-        <v>311.8346198394665</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y21" t="n">
-        <v>232.6513948231691</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="22">
@@ -5919,13 +5919,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P22" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R22" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S22" t="n">
         <v>51.92</v>
@@ -5956,40 +5956,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>597.1205880922939</v>
+        <v>597.1205880922942</v>
       </c>
       <c r="C23" t="n">
-        <v>467.3482868367445</v>
+        <v>467.3482868367447</v>
       </c>
       <c r="D23" t="n">
-        <v>377.1067153823507</v>
+        <v>377.106715382351</v>
       </c>
       <c r="E23" t="n">
-        <v>292.9013723451097</v>
+        <v>292.9013723451099</v>
       </c>
       <c r="F23" t="n">
-        <v>208.1643736501482</v>
+        <v>208.1643736501484</v>
       </c>
       <c r="G23" t="n">
-        <v>125.9679517166614</v>
+        <v>125.9679517166617</v>
       </c>
       <c r="H23" t="n">
-        <v>51.92</v>
+        <v>52.3852397629438</v>
       </c>
       <c r="I23" t="n">
         <v>51.92</v>
       </c>
       <c r="J23" t="n">
-        <v>133.4268380887174</v>
+        <v>559.4285273090126</v>
       </c>
       <c r="K23" t="n">
-        <v>775.9368380887173</v>
+        <v>733.5813277110226</v>
       </c>
       <c r="L23" t="n">
-        <v>991.9887866314309</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M23" t="n">
-        <v>1009.32297330616</v>
+        <v>1592.143276253736</v>
       </c>
       <c r="N23" t="n">
         <v>1651.83297330616</v>
@@ -6016,16 +6016,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V23" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.587310395321</v>
       </c>
       <c r="W23" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X23" t="n">
-        <v>951.9859877270221</v>
+        <v>951.9859877270223</v>
       </c>
       <c r="Y23" t="n">
-        <v>759.7461567342884</v>
+        <v>759.7461567342887</v>
       </c>
     </row>
     <row r="24">
@@ -6035,22 +6035,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>492.6952769985969</v>
+        <v>1237.102618183067</v>
       </c>
       <c r="C24" t="n">
-        <v>452.1903149324157</v>
+        <v>1196.597656116886</v>
       </c>
       <c r="D24" t="n">
-        <v>424.9805301872615</v>
+        <v>845.1454471293077</v>
       </c>
       <c r="E24" t="n">
-        <v>403.0895228924003</v>
+        <v>499.0120155920222</v>
       </c>
       <c r="F24" t="n">
-        <v>384.2650356824237</v>
+        <v>155.9451041396213</v>
       </c>
       <c r="G24" t="n">
-        <v>55.98259997866057</v>
+        <v>151.9050926782825</v>
       </c>
       <c r="H24" t="n">
         <v>51.92</v>
@@ -6080,31 +6080,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q24" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R24" t="n">
-        <v>2062.032218270268</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S24" t="n">
-        <v>1928.880474452383</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T24" t="n">
-        <v>1846.683151095642</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U24" t="n">
-        <v>1591.376589078594</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V24" t="n">
-        <v>1496.92136969322</v>
+        <v>1592.843862392842</v>
       </c>
       <c r="W24" t="n">
-        <v>1060.180821299454</v>
+        <v>1480.3457382415</v>
       </c>
       <c r="X24" t="n">
-        <v>960.319468324315</v>
+        <v>1380.484385266361</v>
       </c>
       <c r="Y24" t="n">
-        <v>881.1362433080177</v>
+        <v>1301.301160250064</v>
       </c>
     </row>
     <row r="25">
@@ -6156,13 +6156,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P25" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R25" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S25" t="n">
         <v>51.92</v>
@@ -6220,22 +6220,22 @@
         <v>133.4268380887174</v>
       </c>
       <c r="K26" t="n">
-        <v>307.5796384907274</v>
+        <v>737.2059437357115</v>
       </c>
       <c r="L26" t="n">
-        <v>523.631587033441</v>
+        <v>953.2578922784251</v>
       </c>
       <c r="M26" t="n">
-        <v>1009.32297330616</v>
+        <v>1595.767892278425</v>
       </c>
       <c r="N26" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O26" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P26" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q26" t="n">
         <v>2596</v>
@@ -6272,25 +6272,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>362.0396347695416</v>
+        <v>912.8601939406431</v>
       </c>
       <c r="C27" t="n">
-        <v>321.5346727033605</v>
+        <v>548.1128076320376</v>
       </c>
       <c r="D27" t="n">
-        <v>294.3248879582063</v>
+        <v>196.6605986444592</v>
       </c>
       <c r="E27" t="n">
-        <v>272.4338806633451</v>
+        <v>174.769591349598</v>
       </c>
       <c r="F27" t="n">
-        <v>253.6093934533685</v>
+        <v>155.9451041396213</v>
       </c>
       <c r="G27" t="n">
-        <v>249.5693819920296</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H27" t="n">
-        <v>245.506782013369</v>
+        <v>51.92</v>
       </c>
       <c r="I27" t="n">
         <v>51.92</v>
@@ -6317,31 +6317,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q27" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R27" t="n">
-        <v>1756.031307473563</v>
+        <v>1982.60944240224</v>
       </c>
       <c r="S27" t="n">
-        <v>1622.879563655679</v>
+        <v>1849.457698584356</v>
       </c>
       <c r="T27" t="n">
-        <v>1540.682240298937</v>
+        <v>1767.260375227614</v>
       </c>
       <c r="U27" t="n">
-        <v>1460.720946849539</v>
+        <v>1687.299081778216</v>
       </c>
       <c r="V27" t="n">
-        <v>1366.265727464165</v>
+        <v>1268.601438150418</v>
       </c>
       <c r="W27" t="n">
-        <v>929.5251790703988</v>
+        <v>1156.103313999076</v>
       </c>
       <c r="X27" t="n">
-        <v>829.6638260952599</v>
+        <v>1056.241961023937</v>
       </c>
       <c r="Y27" t="n">
-        <v>750.4806010789625</v>
+        <v>977.0587360076396</v>
       </c>
     </row>
     <row r="28">
@@ -6381,25 +6381,25 @@
         <v>1619.080700024145</v>
       </c>
       <c r="L28" t="n">
-        <v>1608.654647405756</v>
+        <v>1609.501360385148</v>
       </c>
       <c r="M28" t="n">
-        <v>1505.227982468588</v>
+        <v>1506.07469544798</v>
       </c>
       <c r="N28" t="n">
-        <v>1348.401726605486</v>
+        <v>1349.248439584877</v>
       </c>
       <c r="O28" t="n">
-        <v>1114.295626111697</v>
+        <v>1115.142339091088</v>
       </c>
       <c r="P28" t="n">
-        <v>819.9299076645211</v>
+        <v>820.7766206439126</v>
       </c>
       <c r="Q28" t="n">
-        <v>463.4700425881595</v>
+        <v>464.3167555675508</v>
       </c>
       <c r="R28" t="n">
-        <v>81.94485949741244</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S28" t="n">
         <v>51.92</v>
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>596.6553483293503</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C29" t="n">
-        <v>466.8830470738009</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D29" t="n">
-        <v>376.6414756194072</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E29" t="n">
-        <v>292.4361325821661</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F29" t="n">
-        <v>207.6991338872047</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G29" t="n">
-        <v>125.5027119537179</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H29" t="n">
         <v>51.92</v>
@@ -6457,19 +6457,19 @@
         <v>559.4285273090126</v>
       </c>
       <c r="K29" t="n">
-        <v>1201.938527309012</v>
+        <v>989.863031102066</v>
       </c>
       <c r="L29" t="n">
-        <v>1417.990475851726</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="M29" t="n">
-        <v>1651.83297330616</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="N29" t="n">
-        <v>1651.83297330616</v>
+        <v>1205.91497964478</v>
       </c>
       <c r="O29" t="n">
-        <v>1812.963074689115</v>
+        <v>1367.045081027735</v>
       </c>
       <c r="P29" t="n">
         <v>2009.555081027735</v>
@@ -6478,28 +6478,28 @@
         <v>2596</v>
       </c>
       <c r="R29" t="n">
-        <v>2595.534760237057</v>
+        <v>2596</v>
       </c>
       <c r="S29" t="n">
-        <v>2451.762030971221</v>
+        <v>2452.227270734164</v>
       </c>
       <c r="T29" t="n">
-        <v>2189.517714621877</v>
+        <v>2189.982954384821</v>
       </c>
       <c r="U29" t="n">
-        <v>1858.092802114017</v>
+        <v>1858.558041876961</v>
       </c>
       <c r="V29" t="n">
-        <v>1546.122070632377</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W29" t="n">
-        <v>1225.542801964753</v>
+        <v>1226.008041727697</v>
       </c>
       <c r="X29" t="n">
-        <v>951.5207479640785</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y29" t="n">
-        <v>759.2809169713448</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="30">
@@ -6509,22 +6509,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>816.9377012410212</v>
+        <v>492.6952769985968</v>
       </c>
       <c r="C30" t="n">
-        <v>452.1903149324157</v>
+        <v>127.9478906899915</v>
       </c>
       <c r="D30" t="n">
-        <v>424.9805301872615</v>
+        <v>100.7381059448373</v>
       </c>
       <c r="E30" t="n">
         <v>78.84709864997603</v>
       </c>
       <c r="F30" t="n">
-        <v>60.0226114399994</v>
+        <v>60.02261143999941</v>
       </c>
       <c r="G30" t="n">
-        <v>55.98259997866058</v>
+        <v>55.98259997866057</v>
       </c>
       <c r="H30" t="n">
         <v>51.92</v>
@@ -6563,7 +6563,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T30" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U30" t="n">
         <v>1766.721857646244</v>
@@ -6572,13 +6572,13 @@
         <v>1496.92136969322</v>
       </c>
       <c r="W30" t="n">
-        <v>1384.423245541878</v>
+        <v>1060.180821299454</v>
       </c>
       <c r="X30" t="n">
-        <v>1284.561892566739</v>
+        <v>960.3194683243149</v>
       </c>
       <c r="Y30" t="n">
-        <v>881.1362433080177</v>
+        <v>881.1362433080176</v>
       </c>
     </row>
     <row r="31">
@@ -6630,13 +6630,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P31" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q31" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R31" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S31" t="n">
         <v>51.92</v>
@@ -6667,10 +6667,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>597.1205880922942</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C32" t="n">
-        <v>467.3482868367447</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D32" t="n">
         <v>376.6414756194072</v>
@@ -6697,16 +6697,16 @@
         <v>733.5813277110226</v>
       </c>
       <c r="L32" t="n">
-        <v>1205.91497964478</v>
+        <v>949.6332762537361</v>
       </c>
       <c r="M32" t="n">
-        <v>1205.91497964478</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N32" t="n">
-        <v>1205.91497964478</v>
+        <v>1651.83297330616</v>
       </c>
       <c r="O32" t="n">
-        <v>1367.045081027735</v>
+        <v>1812.963074689115</v>
       </c>
       <c r="P32" t="n">
         <v>2009.555081027735</v>
@@ -6718,25 +6718,25 @@
         <v>2596</v>
       </c>
       <c r="S32" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T32" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U32" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V32" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W32" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X32" t="n">
-        <v>951.9859877270223</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y32" t="n">
-        <v>759.7461567342887</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="33">
@@ -6746,22 +6746,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1141.180125483445</v>
+        <v>1316.525394051095</v>
       </c>
       <c r="C33" t="n">
-        <v>776.43273917484</v>
+        <v>1276.020431984914</v>
       </c>
       <c r="D33" t="n">
-        <v>424.9805301872615</v>
+        <v>924.5682229973352</v>
       </c>
       <c r="E33" t="n">
-        <v>78.84709864997603</v>
+        <v>578.4347914600496</v>
       </c>
       <c r="F33" t="n">
-        <v>60.0226114399994</v>
+        <v>235.3678800076487</v>
       </c>
       <c r="G33" t="n">
-        <v>55.98259997866058</v>
+        <v>231.3278685463099</v>
       </c>
       <c r="H33" t="n">
         <v>51.92</v>
@@ -6858,16 +6858,16 @@
         <v>1608.654647405756</v>
       </c>
       <c r="M34" t="n">
-        <v>1506.07469544798</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N34" t="n">
-        <v>1349.248439584877</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O34" t="n">
-        <v>1115.142339091088</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P34" t="n">
-        <v>820.7766206439126</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q34" t="n">
         <v>464.3167555675508</v>
@@ -6916,7 +6916,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F35" t="n">
-        <v>207.6991338872047</v>
+        <v>207.6991338872046</v>
       </c>
       <c r="G35" t="n">
         <v>125.5027119537179</v>
@@ -6952,13 +6952,13 @@
         <v>2596</v>
       </c>
       <c r="R35" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S35" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T35" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U35" t="n">
         <v>1858.092802114017</v>
@@ -6983,22 +6983,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>343.7981213238219</v>
+        <v>992.2829698086708</v>
       </c>
       <c r="C36" t="n">
-        <v>127.9478906899915</v>
+        <v>951.7780077424898</v>
       </c>
       <c r="D36" t="n">
-        <v>100.7381059448373</v>
+        <v>924.5682229973356</v>
       </c>
       <c r="E36" t="n">
-        <v>78.84709864997603</v>
+        <v>578.4347914600501</v>
       </c>
       <c r="F36" t="n">
-        <v>60.0226114399994</v>
+        <v>235.3678800076491</v>
       </c>
       <c r="G36" t="n">
-        <v>55.98259997866058</v>
+        <v>231.3278685463103</v>
       </c>
       <c r="H36" t="n">
         <v>51.92</v>
@@ -7037,22 +7037,22 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T36" t="n">
-        <v>1846.683151095641</v>
+        <v>1846.683151095642</v>
       </c>
       <c r="U36" t="n">
         <v>1766.721857646244</v>
       </c>
       <c r="V36" t="n">
-        <v>1672.26663826087</v>
+        <v>1348.024214018445</v>
       </c>
       <c r="W36" t="n">
-        <v>1235.526089867103</v>
+        <v>1235.526089867104</v>
       </c>
       <c r="X36" t="n">
-        <v>1135.664736891964</v>
+        <v>1135.664736891965</v>
       </c>
       <c r="Y36" t="n">
-        <v>732.2390876332428</v>
+        <v>1056.481511875667</v>
       </c>
     </row>
     <row r="37">
@@ -7104,13 +7104,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P37" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q37" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R37" t="n">
-        <v>81.94485949741244</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S37" t="n">
         <v>51.92</v>
@@ -7141,25 +7141,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>597.1205880922939</v>
+        <v>596.6553483293503</v>
       </c>
       <c r="C38" t="n">
-        <v>467.3482868367445</v>
+        <v>466.8830470738009</v>
       </c>
       <c r="D38" t="n">
-        <v>377.1067153823507</v>
+        <v>376.6414756194072</v>
       </c>
       <c r="E38" t="n">
-        <v>292.9013723451097</v>
+        <v>292.4361325821661</v>
       </c>
       <c r="F38" t="n">
-        <v>208.1643736501482</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G38" t="n">
-        <v>125.9679517166614</v>
+        <v>125.5027119537179</v>
       </c>
       <c r="H38" t="n">
-        <v>52.38523976294358</v>
+        <v>51.92</v>
       </c>
       <c r="I38" t="n">
         <v>51.92</v>
@@ -7174,7 +7174,7 @@
         <v>949.6332762537361</v>
       </c>
       <c r="M38" t="n">
-        <v>1592.143276253736</v>
+        <v>1009.32297330616</v>
       </c>
       <c r="N38" t="n">
         <v>1651.83297330616</v>
@@ -7189,28 +7189,28 @@
         <v>2596</v>
       </c>
       <c r="R38" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S38" t="n">
-        <v>2452.227270734164</v>
+        <v>2451.762030971221</v>
       </c>
       <c r="T38" t="n">
-        <v>2189.982954384821</v>
+        <v>2189.517714621877</v>
       </c>
       <c r="U38" t="n">
-        <v>1858.558041876961</v>
+        <v>1858.092802114017</v>
       </c>
       <c r="V38" t="n">
-        <v>1546.58731039532</v>
+        <v>1546.122070632377</v>
       </c>
       <c r="W38" t="n">
-        <v>1226.008041727697</v>
+        <v>1225.542801964753</v>
       </c>
       <c r="X38" t="n">
-        <v>951.9859877270221</v>
+        <v>951.5207479640785</v>
       </c>
       <c r="Y38" t="n">
-        <v>759.7461567342884</v>
+        <v>759.2809169713448</v>
       </c>
     </row>
     <row r="39">
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>992.2829698086708</v>
+        <v>1010.52448325439</v>
       </c>
       <c r="C39" t="n">
-        <v>627.5355835000655</v>
+        <v>970.019521188209</v>
       </c>
       <c r="D39" t="n">
-        <v>600.3257987549114</v>
+        <v>942.8097364430548</v>
       </c>
       <c r="E39" t="n">
-        <v>254.1923672176259</v>
+        <v>596.6763049057694</v>
       </c>
       <c r="F39" t="n">
-        <v>235.3678800076492</v>
+        <v>253.6093934533685</v>
       </c>
       <c r="G39" t="n">
-        <v>55.98259997866057</v>
+        <v>249.5693819920296</v>
       </c>
       <c r="H39" t="n">
-        <v>51.92</v>
+        <v>245.506782013369</v>
       </c>
       <c r="I39" t="n">
         <v>51.92</v>
@@ -7274,7 +7274,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T39" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U39" t="n">
         <v>1766.721857646244</v>
@@ -7283,13 +7283,13 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W39" t="n">
-        <v>1559.768514109528</v>
+        <v>1253.767603312823</v>
       </c>
       <c r="X39" t="n">
-        <v>1459.907161134389</v>
+        <v>1153.906250337684</v>
       </c>
       <c r="Y39" t="n">
-        <v>1056.481511875667</v>
+        <v>1074.723025321387</v>
       </c>
     </row>
     <row r="40">
@@ -7341,13 +7341,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P40" t="n">
-        <v>819.9299076645212</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q40" t="n">
-        <v>463.4700425881596</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R40" t="n">
-        <v>81.94485949741255</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S40" t="n">
         <v>51.92</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>597.1205880922942</v>
+        <v>597.1205880922939</v>
       </c>
       <c r="C41" t="n">
-        <v>467.3482868367447</v>
+        <v>467.3482868367445</v>
       </c>
       <c r="D41" t="n">
-        <v>377.106715382351</v>
+        <v>377.1067153823507</v>
       </c>
       <c r="E41" t="n">
-        <v>292.9013723451099</v>
+        <v>292.9013723451097</v>
       </c>
       <c r="F41" t="n">
-        <v>208.1643736501484</v>
+        <v>208.1643736501482</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9679517166617</v>
+        <v>125.9679517166614</v>
       </c>
       <c r="H41" t="n">
         <v>51.92</v>
@@ -7402,25 +7402,25 @@
         <v>51.92</v>
       </c>
       <c r="J41" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K41" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L41" t="n">
-        <v>949.6332762537361</v>
+        <v>991.9887866314309</v>
       </c>
       <c r="M41" t="n">
-        <v>1592.143276253736</v>
+        <v>1634.498786631431</v>
       </c>
       <c r="N41" t="n">
-        <v>1651.83297330616</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O41" t="n">
-        <v>1812.963074689115</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P41" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q41" t="n">
         <v>2596</v>
@@ -7438,16 +7438,16 @@
         <v>1858.558041876961</v>
       </c>
       <c r="V41" t="n">
-        <v>1546.587310395321</v>
+        <v>1546.58731039532</v>
       </c>
       <c r="W41" t="n">
         <v>1226.008041727697</v>
       </c>
       <c r="X41" t="n">
-        <v>951.9859877270223</v>
+        <v>951.9859877270221</v>
       </c>
       <c r="Y41" t="n">
-        <v>759.7461567342887</v>
+        <v>759.7461567342884</v>
       </c>
     </row>
     <row r="42">
@@ -7457,25 +7457,25 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>816.9377012410212</v>
+        <v>1010.52448325439</v>
       </c>
       <c r="C42" t="n">
-        <v>452.1903149324158</v>
+        <v>970.019521188209</v>
       </c>
       <c r="D42" t="n">
-        <v>424.9805301872616</v>
+        <v>942.8097364430548</v>
       </c>
       <c r="E42" t="n">
-        <v>403.0895228924003</v>
+        <v>596.6763049057694</v>
       </c>
       <c r="F42" t="n">
-        <v>60.0226114399994</v>
+        <v>253.6093934533685</v>
       </c>
       <c r="G42" t="n">
-        <v>55.98259997866058</v>
+        <v>249.5693819920296</v>
       </c>
       <c r="H42" t="n">
-        <v>51.92</v>
+        <v>245.506782013369</v>
       </c>
       <c r="I42" t="n">
         <v>51.92</v>
@@ -7502,31 +7502,31 @@
         <v>2244.187340368535</v>
       </c>
       <c r="Q42" t="n">
-        <v>2244.187340368535</v>
+        <v>2164.764564500508</v>
       </c>
       <c r="R42" t="n">
-        <v>2062.032218270268</v>
+        <v>1756.031307473563</v>
       </c>
       <c r="S42" t="n">
-        <v>1928.880474452383</v>
+        <v>1622.879563655678</v>
       </c>
       <c r="T42" t="n">
-        <v>1846.683151095641</v>
+        <v>1540.682240298936</v>
       </c>
       <c r="U42" t="n">
-        <v>1766.721857646244</v>
+        <v>1460.720946849539</v>
       </c>
       <c r="V42" t="n">
-        <v>1496.92136969322</v>
+        <v>1366.265727464165</v>
       </c>
       <c r="W42" t="n">
-        <v>1060.180821299454</v>
+        <v>1253.767603312823</v>
       </c>
       <c r="X42" t="n">
-        <v>960.319468324315</v>
+        <v>1153.906250337684</v>
       </c>
       <c r="Y42" t="n">
-        <v>881.1362433080177</v>
+        <v>1074.723025321387</v>
       </c>
     </row>
     <row r="43">
@@ -7578,13 +7578,13 @@
         <v>1114.295626111697</v>
       </c>
       <c r="P43" t="n">
-        <v>819.9299076645211</v>
+        <v>819.9299076645212</v>
       </c>
       <c r="Q43" t="n">
-        <v>463.4700425881595</v>
+        <v>463.4700425881596</v>
       </c>
       <c r="R43" t="n">
-        <v>82.79157247680381</v>
+        <v>81.94485949741255</v>
       </c>
       <c r="S43" t="n">
         <v>51.92</v>
@@ -7627,7 +7627,7 @@
         <v>292.4361325821661</v>
       </c>
       <c r="F44" t="n">
-        <v>207.6991338872046</v>
+        <v>207.6991338872047</v>
       </c>
       <c r="G44" t="n">
         <v>125.5027119537179</v>
@@ -7639,31 +7639,31 @@
         <v>51.92</v>
       </c>
       <c r="J44" t="n">
-        <v>559.4285273090126</v>
+        <v>133.4268380887174</v>
       </c>
       <c r="K44" t="n">
-        <v>733.5813277110226</v>
+        <v>775.9368380887173</v>
       </c>
       <c r="L44" t="n">
-        <v>949.6332762537361</v>
+        <v>1418.446838088717</v>
       </c>
       <c r="M44" t="n">
-        <v>949.6332762537362</v>
+        <v>2060.956838088718</v>
       </c>
       <c r="N44" t="n">
-        <v>1205.91497964478</v>
+        <v>2238.277892278425</v>
       </c>
       <c r="O44" t="n">
-        <v>1367.045081027735</v>
+        <v>2399.40799366138</v>
       </c>
       <c r="P44" t="n">
-        <v>2009.555081027735</v>
+        <v>2596</v>
       </c>
       <c r="Q44" t="n">
         <v>2596</v>
       </c>
       <c r="R44" t="n">
-        <v>2596</v>
+        <v>2595.534760237057</v>
       </c>
       <c r="S44" t="n">
         <v>2451.762030971221</v>
@@ -7694,22 +7694,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>668.0405455662465</v>
+        <v>668.040545566246</v>
       </c>
       <c r="C45" t="n">
-        <v>303.2931592576411</v>
+        <v>303.2931592576406</v>
       </c>
       <c r="D45" t="n">
-        <v>276.0833745124869</v>
+        <v>276.0833745124864</v>
       </c>
       <c r="E45" t="n">
         <v>78.84709864997603</v>
       </c>
       <c r="F45" t="n">
-        <v>60.02261143999941</v>
+        <v>60.0226114399994</v>
       </c>
       <c r="G45" t="n">
-        <v>55.98259997866057</v>
+        <v>55.98259997866058</v>
       </c>
       <c r="H45" t="n">
         <v>51.92</v>
@@ -7748,7 +7748,7 @@
         <v>1928.880474452383</v>
       </c>
       <c r="T45" t="n">
-        <v>1846.683151095642</v>
+        <v>1846.683151095641</v>
       </c>
       <c r="U45" t="n">
         <v>1766.721857646244</v>
@@ -7757,10 +7757,10 @@
         <v>1672.26663826087</v>
       </c>
       <c r="W45" t="n">
-        <v>1235.526089867104</v>
+        <v>1559.768514109528</v>
       </c>
       <c r="X45" t="n">
-        <v>1135.664736891965</v>
+        <v>1459.907161134389</v>
       </c>
       <c r="Y45" t="n">
         <v>1056.481511875667</v>
@@ -7797,31 +7797,31 @@
         <v>1189.283805434826</v>
       </c>
       <c r="J46" t="n">
-        <v>1515.576154611957</v>
+        <v>1515.576154611867</v>
       </c>
       <c r="K46" t="n">
-        <v>1619.080700024235</v>
+        <v>1619.080700024145</v>
       </c>
       <c r="L46" t="n">
-        <v>1608.654647405846</v>
+        <v>1608.654647405756</v>
       </c>
       <c r="M46" t="n">
-        <v>1505.227982468678</v>
+        <v>1505.227982468588</v>
       </c>
       <c r="N46" t="n">
-        <v>1348.401726605575</v>
+        <v>1348.401726605486</v>
       </c>
       <c r="O46" t="n">
-        <v>1114.295626111786</v>
+        <v>1114.295626111697</v>
       </c>
       <c r="P46" t="n">
-        <v>819.9299076646108</v>
+        <v>819.9299076645211</v>
       </c>
       <c r="Q46" t="n">
-        <v>463.4700425882492</v>
+        <v>463.4700425881595</v>
       </c>
       <c r="R46" t="n">
-        <v>81.94485949750214</v>
+        <v>82.79157247680381</v>
       </c>
       <c r="S46" t="n">
         <v>51.92</v>
@@ -7964,25 +7964,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>309.2909949748744</v>
       </c>
       <c r="M2" t="n">
-        <v>766.440775325176</v>
+        <v>720.3111720492747</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O2" t="n">
-        <v>375.1590153027356</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P2" t="n">
-        <v>315.3213213472141</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>128.5418702571336</v>
@@ -8201,10 +8201,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>300.4507139686307</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K5" t="n">
-        <v>321.8400703517588</v>
+        <v>248.0502805878618</v>
       </c>
       <c r="L5" t="n">
         <v>309.2909949748744</v>
@@ -8213,7 +8213,7 @@
         <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
         <v>1.159015302735668</v>
@@ -8450,16 +8450,16 @@
         <v>846.2608914614127</v>
       </c>
       <c r="N8" t="n">
-        <v>587.423942175285</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>184.500290865472</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>502.5418702571336</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,16 +8675,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>179.1121759491998</v>
       </c>
       <c r="K11" t="n">
-        <v>473.08808040201</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L11" t="n">
         <v>430.7657085427136</v>
       </c>
       <c r="M11" t="n">
-        <v>699.241868512898</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N11" t="n">
         <v>230.4920535472222</v>
@@ -8915,16 +8915,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K14" t="n">
-        <v>278.5269147425628</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>430.7657085427136</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N14" t="n">
-        <v>230.4920535472222</v>
+        <v>290.7846768324985</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -9158,16 +9158,16 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>341.6095732017122</v>
+        <v>305.789467185889</v>
       </c>
       <c r="N17" t="n">
         <v>879.4920535472222</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>486.2423218353989</v>
       </c>
       <c r="P17" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9386,25 +9386,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N20" t="n">
-        <v>230.4920535472222</v>
+        <v>290.7846768324985</v>
       </c>
       <c r="O20" t="n">
-        <v>216.0870636498472</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9623,19 +9623,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>473.0880804020101</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>318.9437086192779</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N23" t="n">
-        <v>879.4920535472222</v>
+        <v>290.7846768324985</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -9863,13 +9863,13 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>433.9659648939233</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>792.031789021288</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N26" t="n">
         <v>879.4920535472222</v>
@@ -9881,7 +9881,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,13 +10100,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>473.08808040201</v>
+        <v>258.8704074657004</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>537.6389720331213</v>
+        <v>301.434429149855</v>
       </c>
       <c r="N29" t="n">
         <v>230.4920535472222</v>
@@ -10115,7 +10115,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>450.422215819576</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10340,19 +10340,19 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>258.8704074657004</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>301.434429149855</v>
+        <v>361.7270524351312</v>
       </c>
       <c r="N32" t="n">
-        <v>230.4920535472222</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10817,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>950.4344291498551</v>
+        <v>361.7270524351312</v>
       </c>
       <c r="N38" t="n">
-        <v>290.7846768324985</v>
+        <v>879.4920535472222</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -11045,10 +11045,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11057,7 +11057,7 @@
         <v>950.4344291498551</v>
       </c>
       <c r="N41" t="n">
-        <v>290.7846768324985</v>
+        <v>840.3699380391354</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11066,7 +11066,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11282,28 +11282,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>473.0880804020101</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>430.7657085427136</v>
       </c>
       <c r="M44" t="n">
-        <v>301.434429149855</v>
+        <v>950.4344291498551</v>
       </c>
       <c r="N44" t="n">
-        <v>489.3624610129226</v>
+        <v>409.6042294964216</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>450.422215819576</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>615.8520732695737</v>
+        <v>23.48346824708341</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -23420,7 +23420,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -23432,7 +23432,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>0.8382458495974596</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23648,10 +23648,10 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8382458495977119</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -23885,7 +23885,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -23900,7 +23900,7 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24377,10 +24377,10 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.8382458495976817</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24617,7 +24617,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.8382458495974596</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24851,10 +24851,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25073,7 +25073,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8382458495977119</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -25085,7 +25085,7 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -25328,7 +25328,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.8382458495974596</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25562,10 +25562,10 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="S40" t="n">
-        <v>0.8382458495973424</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25799,10 +25799,10 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0.8382458495974561</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>0.8382458495973424</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -26036,10 +26036,10 @@
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.8382458495974561</v>
       </c>
       <c r="S46" t="n">
-        <v>0.8382458495086524</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -26272,13 +26272,13 @@
         <v>1322345.892349225</v>
       </c>
       <c r="C2" t="n">
-        <v>1322345.892349224</v>
+        <v>1322345.892349225</v>
       </c>
       <c r="D2" t="n">
         <v>1322345.892349224</v>
       </c>
       <c r="E2" t="n">
-        <v>1322324.768553815</v>
+        <v>1322324.768553814</v>
       </c>
       <c r="F2" t="n">
         <v>1322324.768553814</v>
@@ -26287,7 +26287,7 @@
         <v>1322324.768553814</v>
       </c>
       <c r="H2" t="n">
-        <v>1322324.768553814</v>
+        <v>1322324.768553815</v>
       </c>
       <c r="I2" t="n">
         <v>1322324.768553815</v>
@@ -26296,10 +26296,10 @@
         <v>1322324.768553814</v>
       </c>
       <c r="K2" t="n">
-        <v>1322324.768553814</v>
+        <v>1322324.768553815</v>
       </c>
       <c r="L2" t="n">
-        <v>1322324.768553814</v>
+        <v>1322324.768553815</v>
       </c>
       <c r="M2" t="n">
         <v>1322324.768553815</v>
@@ -26308,10 +26308,10 @@
         <v>1322324.768553815</v>
       </c>
       <c r="O2" t="n">
+        <v>1322324.768553815</v>
+      </c>
+      <c r="P2" t="n">
         <v>1322324.768553814</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1322324.768553817</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>577464.9346667652</v>
+        <v>570963.5697337883</v>
       </c>
       <c r="C4" t="n">
-        <v>575456.0124792766</v>
+        <v>568954.6475462997</v>
       </c>
       <c r="D4" t="n">
-        <v>573444.3650634525</v>
+        <v>566943.0001304757</v>
       </c>
       <c r="E4" t="n">
-        <v>489938.979796175</v>
+        <v>483475.9886658207</v>
       </c>
       <c r="F4" t="n">
-        <v>488252.9169779521</v>
+        <v>481789.9258475979</v>
       </c>
       <c r="G4" t="n">
-        <v>486564.5274562991</v>
+        <v>480101.5363259449</v>
       </c>
       <c r="H4" t="n">
-        <v>484873.7945463364</v>
+        <v>478410.8034159822</v>
       </c>
       <c r="I4" t="n">
-        <v>483180.7013457892</v>
+        <v>476717.7102154349</v>
       </c>
       <c r="J4" t="n">
-        <v>481485.2307308645</v>
+        <v>475022.2396005102</v>
       </c>
       <c r="K4" t="n">
-        <v>479787.365352031</v>
+        <v>473324.3742216767</v>
       </c>
       <c r="L4" t="n">
-        <v>478087.087629687</v>
+        <v>471624.0964993328</v>
       </c>
       <c r="M4" t="n">
-        <v>476384.3797497193</v>
+        <v>469921.3886193651</v>
       </c>
       <c r="N4" t="n">
-        <v>474679.2236589554</v>
+        <v>468216.2325286013</v>
       </c>
       <c r="O4" t="n">
-        <v>472971.6010604933</v>
+        <v>466508.6099301392</v>
       </c>
       <c r="P4" t="n">
-        <v>471261.493408911</v>
+        <v>464798.5022785557</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>455192.5576824594</v>
+        <v>461693.9226154363</v>
       </c>
       <c r="C6" t="n">
-        <v>688299.4798699474</v>
+        <v>694800.8448029248</v>
       </c>
       <c r="D6" t="n">
-        <v>690311.1272857715</v>
+        <v>696812.4922187485</v>
       </c>
       <c r="E6" t="n">
-        <v>168891.2397576399</v>
+        <v>175354.2308879934</v>
       </c>
       <c r="F6" t="n">
-        <v>760127.3025758623</v>
+        <v>766590.2937062163</v>
       </c>
       <c r="G6" t="n">
-        <v>761815.6920975153</v>
+        <v>768278.6832278692</v>
       </c>
       <c r="H6" t="n">
-        <v>763506.425007478</v>
+        <v>769969.4161378331</v>
       </c>
       <c r="I6" t="n">
-        <v>765199.5182080256</v>
+        <v>771662.5093383797</v>
       </c>
       <c r="J6" t="n">
-        <v>378446.9888229499</v>
+        <v>384909.9799533042</v>
       </c>
       <c r="K6" t="n">
-        <v>768592.8542017834</v>
+        <v>775055.8453321381</v>
       </c>
       <c r="L6" t="n">
-        <v>770293.1319241273</v>
+        <v>776756.1230544818</v>
       </c>
       <c r="M6" t="n">
-        <v>675195.8398040956</v>
+        <v>681658.8309344503</v>
       </c>
       <c r="N6" t="n">
-        <v>773700.9958948594</v>
+        <v>780163.9870252133</v>
       </c>
       <c r="O6" t="n">
-        <v>518608.618493321</v>
+        <v>525071.6096236759</v>
       </c>
       <c r="P6" t="n">
-        <v>777118.7261449064</v>
+        <v>783581.7172752585</v>
       </c>
     </row>
   </sheetData>
@@ -26972,10 +26972,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>-0</v>
@@ -27005,7 +27005,7 @@
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
@@ -27518,16 +27518,16 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>187.0595574316536</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>330.0491815260438</v>
@@ -27569,10 +27569,10 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>276.1269185778543</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>40.51066719152016</v>
+        <v>400</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27609,16 +27609,16 @@
         <v>244.8599384153005</v>
       </c>
       <c r="H4" t="n">
+        <v>227.1357818393235</v>
+      </c>
+      <c r="I4" t="n">
         <v>400</v>
       </c>
-      <c r="I4" t="n">
-        <v>171.1020457840527</v>
-      </c>
       <c r="J4" t="n">
-        <v>27.68234559992325</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K4" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>396.2015953708939</v>
@@ -27642,7 +27642,7 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
         <v>400</v>
@@ -27657,10 +27657,10 @@
         <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>288.2374138222972</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>398.2013121321734</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033002</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27755,13 +27755,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.5201396486123</v>
@@ -27794,10 +27794,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27806,19 +27806,19 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
-        <v>400</v>
+        <v>26.1959257979226</v>
       </c>
       <c r="V6" t="n">
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>58.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>286.003989697443</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>294.589761420123</v>
       </c>
     </row>
     <row r="7">
@@ -27828,10 +27828,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>392.4628641011657</v>
+        <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D7" t="n">
         <v>285.5362180555555</v>
@@ -27843,10 +27843,10 @@
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>400</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H7" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I7" t="n">
         <v>400</v>
@@ -27882,22 +27882,22 @@
         <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>209.2386648669134</v>
+        <v>286.984896591008</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X7" t="n">
         <v>400</v>
       </c>
-      <c r="X7" t="n">
-        <v>247.4436454301076</v>
-      </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033003</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27958,7 +27958,7 @@
         <v>225.120779732817</v>
       </c>
       <c r="S8" t="n">
-        <v>398.2013121321733</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27986,7 +27986,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>255.5856002110573</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -27995,10 +27995,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
         <v>325.5201396486123</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.06671792211793</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28065,13 +28065,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>280.9809048369565</v>
@@ -28083,13 +28083,13 @@
         <v>244.8599384153005</v>
       </c>
       <c r="H10" t="n">
-        <v>313.1591266895974</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>22.26478490148153</v>
+        <v>336.4010833597353</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28128,7 +28128,7 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>400</v>
@@ -28229,13 +28229,13 @@
         <v>321</v>
       </c>
       <c r="D12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>321</v>
@@ -28244,7 +28244,7 @@
         <v>321</v>
       </c>
       <c r="I12" t="n">
-        <v>18.05909831126235</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28268,7 +28268,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>321</v>
@@ -28280,16 +28280,16 @@
         <v>321</v>
       </c>
       <c r="U12" t="n">
-        <v>321</v>
+        <v>226.0367322273742</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X12" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>321</v>
@@ -28460,28 +28460,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E15" t="n">
         <v>321</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>147.4081841180273</v>
       </c>
       <c r="G15" t="n">
         <v>321</v>
       </c>
       <c r="H15" t="n">
-        <v>96.68764642060955</v>
+        <v>321</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -28505,7 +28505,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>78.62854810934749</v>
       </c>
       <c r="R15" t="n">
         <v>321</v>
@@ -28529,7 +28529,7 @@
         <v>321</v>
       </c>
       <c r="Y15" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -28636,10 +28636,10 @@
         <v>321</v>
       </c>
       <c r="H17" t="n">
-        <v>321</v>
+        <v>320.5394126346856</v>
       </c>
       <c r="I17" t="n">
-        <v>96.3057582470185</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28697,16 +28697,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>321</v>
+        <v>147.4081841180271</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F18" t="n">
         <v>321</v>
@@ -28754,7 +28754,7 @@
         <v>321</v>
       </c>
       <c r="U18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>321</v>
@@ -28763,10 +28763,10 @@
         <v>321</v>
       </c>
       <c r="X18" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="Y18" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -28876,7 +28876,7 @@
         <v>321</v>
       </c>
       <c r="I20" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470187</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S20" t="n">
         <v>321</v>
@@ -28940,13 +28940,13 @@
         <v>321</v>
       </c>
       <c r="D21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>321</v>
+        <v>147.4081841180267</v>
       </c>
       <c r="G21" t="n">
         <v>321</v>
@@ -28991,13 +28991,13 @@
         <v>321</v>
       </c>
       <c r="U21" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -29110,10 +29110,10 @@
         <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>320.5394126346858</v>
+        <v>321</v>
       </c>
       <c r="I23" t="n">
-        <v>96.76634561233286</v>
+        <v>96.3057582470185</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29171,25 +29171,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C24" t="n">
         <v>321</v>
       </c>
       <c r="D24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="H24" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="I24" t="n">
         <v>191.6509141932353</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>321</v>
@@ -29228,13 +29228,13 @@
         <v>321</v>
       </c>
       <c r="U24" t="n">
-        <v>147.4081841180269</v>
+        <v>321</v>
       </c>
       <c r="V24" t="n">
         <v>321</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X24" t="n">
         <v>321</v>
@@ -29408,13 +29408,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>321</v>
@@ -29423,13 +29423,13 @@
         <v>321</v>
       </c>
       <c r="G27" t="n">
-        <v>321</v>
+        <v>226.0367322273743</v>
       </c>
       <c r="H27" t="n">
         <v>321</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>191.6509141932353</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29453,10 +29453,10 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>18.05909831126246</v>
+        <v>321</v>
       </c>
       <c r="S27" t="n">
         <v>321</v>
@@ -29468,10 +29468,10 @@
         <v>321</v>
       </c>
       <c r="V27" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X27" t="n">
         <v>321</v>
@@ -29584,7 +29584,7 @@
         <v>321</v>
       </c>
       <c r="H29" t="n">
-        <v>321</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I29" t="n">
         <v>96.76634561233286</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>163.5485039252921</v>
+        <v>164.009091290606</v>
       </c>
       <c r="S29" t="n">
         <v>321</v>
@@ -29645,7 +29645,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
@@ -29654,7 +29654,7 @@
         <v>321</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="F30" t="n">
         <v>321</v>
@@ -29705,16 +29705,16 @@
         <v>321</v>
       </c>
       <c r="V30" t="n">
-        <v>147.4081841180271</v>
+        <v>147.4081841180266</v>
       </c>
       <c r="W30" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>321</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31">
@@ -29809,7 +29809,7 @@
         <v>321</v>
       </c>
       <c r="D32" t="n">
-        <v>320.5394126346856</v>
+        <v>321</v>
       </c>
       <c r="E32" t="n">
         <v>321</v>
@@ -29854,7 +29854,7 @@
         <v>164.009091290606</v>
       </c>
       <c r="S32" t="n">
-        <v>321</v>
+        <v>320.539412634686</v>
       </c>
       <c r="T32" t="n">
         <v>321</v>
@@ -29882,10 +29882,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -29894,13 +29894,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>321</v>
       </c>
       <c r="H33" t="n">
-        <v>321</v>
+        <v>147.4081841180272</v>
       </c>
       <c r="I33" t="n">
         <v>191.6509141932353</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S35" t="n">
         <v>321</v>
@@ -30097,7 +30097,7 @@
         <v>321</v>
       </c>
       <c r="U35" t="n">
-        <v>320.5394126346857</v>
+        <v>321</v>
       </c>
       <c r="V35" t="n">
         <v>321</v>
@@ -30119,25 +30119,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="C36" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="D36" t="n">
         <v>321</v>
       </c>
       <c r="E36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>321</v>
       </c>
       <c r="H36" t="n">
-        <v>321</v>
+        <v>147.4081841180268</v>
       </c>
       <c r="I36" t="n">
         <v>191.6509141932353</v>
@@ -30179,16 +30179,16 @@
         <v>321</v>
       </c>
       <c r="V36" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X36" t="n">
         <v>321</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37">
@@ -30298,7 +30298,7 @@
         <v>321</v>
       </c>
       <c r="I38" t="n">
-        <v>96.3057582470187</v>
+        <v>96.76634561233286</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S38" t="n">
         <v>321</v>
@@ -30359,7 +30359,7 @@
         <v>321</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D39" t="n">
         <v>321</v>
@@ -30368,16 +30368,16 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>147.4081841180267</v>
+        <v>321</v>
       </c>
       <c r="H39" t="n">
         <v>321</v>
       </c>
       <c r="I39" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30419,13 +30419,13 @@
         <v>321</v>
       </c>
       <c r="W39" t="n">
-        <v>321</v>
+        <v>18.05909831126223</v>
       </c>
       <c r="X39" t="n">
         <v>321</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40">
@@ -30532,7 +30532,7 @@
         <v>321</v>
       </c>
       <c r="H41" t="n">
-        <v>320.5394126346856</v>
+        <v>320.5394126346858</v>
       </c>
       <c r="I41" t="n">
         <v>96.76634561233286</v>
@@ -30596,13 +30596,13 @@
         <v>321</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="D42" t="n">
         <v>321</v>
       </c>
       <c r="E42" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -30614,7 +30614,7 @@
         <v>321</v>
       </c>
       <c r="I42" t="n">
-        <v>191.6509141932353</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -30638,10 +30638,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>78.62854810934749</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>321</v>
+        <v>96.68764642060938</v>
       </c>
       <c r="S42" t="n">
         <v>321</v>
@@ -30653,10 +30653,10 @@
         <v>321</v>
       </c>
       <c r="V42" t="n">
-        <v>147.4081841180271</v>
+        <v>321</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X42" t="n">
         <v>321</v>
@@ -30799,10 +30799,10 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>164.009091290606</v>
+        <v>163.5485039252921</v>
       </c>
       <c r="S44" t="n">
-        <v>320.539412634686</v>
+        <v>321</v>
       </c>
       <c r="T44" t="n">
         <v>321</v>
@@ -30839,7 +30839,7 @@
         <v>321</v>
       </c>
       <c r="E45" t="n">
-        <v>147.4081841180269</v>
+        <v>147.4081841180273</v>
       </c>
       <c r="F45" t="n">
         <v>321</v>
@@ -30893,13 +30893,13 @@
         <v>321</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>321</v>
       </c>
       <c r="X45" t="n">
         <v>321</v>
       </c>
       <c r="Y45" t="n">
-        <v>321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -30933,7 +30933,7 @@
         <v>321</v>
       </c>
       <c r="J46" t="n">
-        <v>321.0000000000906</v>
+        <v>321</v>
       </c>
       <c r="K46" t="n">
         <v>321</v>
@@ -34743,25 +34743,25 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
+        <v>52.15992964824119</v>
+      </c>
+      <c r="L2" t="n">
         <v>374</v>
       </c>
-      <c r="L2" t="n">
-        <v>64.70900502512563</v>
-      </c>
       <c r="M2" t="n">
-        <v>294.1798838637633</v>
+        <v>248.0502805878619</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O2" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>374</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -34895,16 +34895,16 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J4" t="n">
-        <v>5.41756069844172</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,7 +34928,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T4" t="n">
         <v>190.7613351330866</v>
@@ -34943,10 +34943,10 @@
         <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>40.7937683921897</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,10 +34980,10 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>300.2102102361031</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>374</v>
+        <v>300.210210236103</v>
       </c>
       <c r="L5" t="n">
         <v>374</v>
@@ -34992,7 +34992,7 @@
         <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -35114,10 +35114,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105.3490637640871</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>228.8979542159473</v>
@@ -35168,22 +35168,22 @@
         <v>40.83199570698063</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>77.74623172409451</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35229,16 +35229,16 @@
         <v>374</v>
       </c>
       <c r="N8" t="n">
-        <v>183.3412755627362</v>
+        <v>374</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>183.3412755627363</v>
       </c>
       <c r="P8" t="n">
         <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,13 +35351,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -35369,13 +35369,13 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>86.02334485027392</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I10" t="n">
         <v>228.8979542159473</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>314.1362984582537</v>
       </c>
       <c r="K10" t="n">
         <v>132.8490622644307</v>
@@ -35414,7 +35414,7 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>152.5563545698924</v>
@@ -35454,16 +35454,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>512.6348760697097</v>
+        <v>261.4423154327527</v>
       </c>
       <c r="K11" t="n">
-        <v>648.9999999999999</v>
+        <v>649</v>
       </c>
       <c r="L11" t="n">
         <v>649</v>
       </c>
       <c r="M11" t="n">
-        <v>397.807439363043</v>
+        <v>649</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -35694,16 +35694,16 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K14" t="n">
-        <v>454.4388343405527</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L14" t="n">
+        <v>218.2342914572864</v>
+      </c>
+      <c r="M14" t="n">
         <v>649</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>60.29262328527629</v>
       </c>
       <c r="O14" t="n">
         <v>162.757678164601</v>
@@ -35937,16 +35937,16 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M17" t="n">
-        <v>40.17514405185721</v>
+        <v>4.355038036033999</v>
       </c>
       <c r="N17" t="n">
         <v>649</v>
       </c>
       <c r="O17" t="n">
-        <v>162.757678164601</v>
+        <v>649</v>
       </c>
       <c r="P17" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q17" t="n">
         <v>592.3686050224903</v>
@@ -36165,25 +36165,25 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K20" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L20" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>60.29262328527629</v>
       </c>
       <c r="O20" t="n">
-        <v>378.8447418144481</v>
+        <v>162.757678164601</v>
       </c>
       <c r="P20" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q20" t="n">
         <v>592.3686050224903</v>
@@ -36317,7 +36317,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H22" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I22" t="n">
         <v>163.0214951995539</v>
@@ -36402,19 +36402,19 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>82.3301394835529</v>
+        <v>512.6348760697097</v>
       </c>
       <c r="K23" t="n">
-        <v>649</v>
+        <v>175.9119195979899</v>
       </c>
       <c r="L23" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M23" t="n">
-        <v>17.50927946942293</v>
+        <v>649</v>
       </c>
       <c r="N23" t="n">
-        <v>649</v>
+        <v>60.29262328527629</v>
       </c>
       <c r="O23" t="n">
         <v>162.757678164601</v>
@@ -36554,7 +36554,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H25" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I25" t="n">
         <v>163.0214951995539</v>
@@ -36642,13 +36642,13 @@
         <v>82.3301394835529</v>
       </c>
       <c r="K26" t="n">
-        <v>175.9119195979899</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="L26" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M26" t="n">
-        <v>490.597359871433</v>
+        <v>649</v>
       </c>
       <c r="N26" t="n">
         <v>649</v>
@@ -36660,7 +36660,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q26" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36879,13 +36879,13 @@
         <v>512.6348760697097</v>
       </c>
       <c r="K29" t="n">
-        <v>648.9999999999999</v>
+        <v>434.7823270636903</v>
       </c>
       <c r="L29" t="n">
         <v>218.2342914572864</v>
       </c>
       <c r="M29" t="n">
-        <v>236.2045428832663</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -36894,7 +36894,7 @@
         <v>162.757678164601</v>
       </c>
       <c r="P29" t="n">
-        <v>198.5777841804241</v>
+        <v>649</v>
       </c>
       <c r="Q29" t="n">
         <v>592.3686050224903</v>
@@ -37028,7 +37028,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H31" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I31" t="n">
         <v>163.0214951995539</v>
@@ -37119,19 +37119,19 @@
         <v>175.9119195979899</v>
       </c>
       <c r="L32" t="n">
-        <v>477.1046989229868</v>
+        <v>218.2342914572864</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>60.29262328527617</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="O32" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P32" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q32" t="n">
         <v>592.3686050224903</v>
@@ -37502,7 +37502,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H37" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I37" t="n">
         <v>163.0214951995539</v>
@@ -37596,10 +37596,10 @@
         <v>218.2342914572864</v>
       </c>
       <c r="M38" t="n">
+        <v>60.29262328527617</v>
+      </c>
+      <c r="N38" t="n">
         <v>649</v>
-      </c>
-      <c r="N38" t="n">
-        <v>60.29262328527629</v>
       </c>
       <c r="O38" t="n">
         <v>162.757678164601</v>
@@ -37739,7 +37739,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H40" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I40" t="n">
         <v>163.0214951995539</v>
@@ -37824,10 +37824,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K41" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L41" t="n">
         <v>218.2342914572864</v>
@@ -37836,7 +37836,7 @@
         <v>649</v>
       </c>
       <c r="N41" t="n">
-        <v>60.29262328527629</v>
+        <v>609.8778844919133</v>
       </c>
       <c r="O41" t="n">
         <v>162.757678164601</v>
@@ -37845,7 +37845,7 @@
         <v>198.5777841804241</v>
       </c>
       <c r="Q41" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37976,7 +37976,7 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H43" t="n">
-        <v>97.74415258690598</v>
+        <v>97.74415258690597</v>
       </c>
       <c r="I43" t="n">
         <v>163.0214951995539</v>
@@ -38061,28 +38061,28 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>512.6348760697097</v>
+        <v>82.3301394835529</v>
       </c>
       <c r="K44" t="n">
-        <v>175.9119195979899</v>
+        <v>649</v>
       </c>
       <c r="L44" t="n">
-        <v>218.2342914572864</v>
+        <v>649</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="N44" t="n">
-        <v>258.8704074657004</v>
+        <v>179.1121759491994</v>
       </c>
       <c r="O44" t="n">
         <v>162.757678164601</v>
       </c>
       <c r="P44" t="n">
-        <v>649</v>
+        <v>198.5777841804241</v>
       </c>
       <c r="Q44" t="n">
-        <v>592.3686050224903</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38213,13 +38213,13 @@
         <v>76.57645502732242</v>
       </c>
       <c r="H46" t="n">
-        <v>97.74415258690597</v>
+        <v>97.74415258690598</v>
       </c>
       <c r="I46" t="n">
         <v>163.0214951995539</v>
       </c>
       <c r="J46" t="n">
-        <v>329.5882314920516</v>
+        <v>329.5882314919611</v>
       </c>
       <c r="K46" t="n">
         <v>104.5500458709881</v>
